--- a/Language/EasyControlLang.xlsx
+++ b/Language/EasyControlLang.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEVELOP\Cplusplus\EasyControl\Language\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEVELOP\Cplusplus\SmaDoTec\Language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBBB781-BE47-4261-89C2-96914E6D2D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEACEE7-E2F6-4638-B3ED-6E8B04292214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22440" yWindow="2190" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EasyControlLang" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11190" uniqueCount="10408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11242" uniqueCount="10460">
   <si>
     <t>Deutsch</t>
   </si>
@@ -31271,6 +31271,163 @@
   </si>
   <si>
     <t>Καθορίστε μέχρι ποιο χρονικό διάστημα στο παρελθόν θα εμφανίζονται τα δεδομένα</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Sollwert ist größer als Bezugsgröße!</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Alarmpegel ist kleiner als Max. Gewicht</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Max. Gewicht ist kleiner als Min. Gewicht</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Min. Gewicht ist grösser als Max. Gewicht</t>
+  </si>
+  <si>
+    <t>Invalid value! Setpoint is greater than reference value!</t>
+  </si>
+  <si>
+    <t>Invalid value! Alarm level is less than maximum weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid value! Maximum weight is less than minimum weight
+</t>
+  </si>
+  <si>
+    <t>Invalid value! Minimum weight is greater than maximum weight</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! La valeur de consigne est supérieure à la valeur de référence !</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! Le seuil d'alarme est inférieur au poids maximal</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! Le poids maximal est inférieur au poids minimal</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! Le poids minimal est supérieur au poids maximal</t>
+  </si>
+  <si>
+    <t>Valore non ammesso! Il valore nominale è superiore al valore di riferimento!</t>
+  </si>
+  <si>
+    <t>Valore non ammesso! Il livello di allarme è inferiore al peso massimo</t>
+  </si>
+  <si>
+    <t>Valore non ammesso! Il peso massimo è inferiore al peso minimo</t>
+  </si>
+  <si>
+    <t>Valore non ammesso! Il peso minimo è superiore al peso massimo</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! De ingestelde waarde is groter dan de referentiewaarde!</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! Het alarmniveau is lager dan het maximale gewicht</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! Het maximale gewicht is lager dan het minimale gewicht</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! Het minimale gewicht is groter dan het maximale gewicht</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Hedef değer, referans değerden büyük!</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Alarm seviyesi, maksimum ağırlıktan daha düşük</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Maksimum ağırlık, minimum ağırlıktan daha düşük</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Minimum ağırlık, maksimum ağırlıktan daha büyük</t>
+  </si>
+  <si>
+    <t>Niedopuszczalna wartość! Wartość zadana jest większa niż wartość odniesienia!</t>
+  </si>
+  <si>
+    <t>Niedopuszczalna wartość! Poziom alarmowy jest mniejszy niż maksymalna waga</t>
+  </si>
+  <si>
+    <t>Niedopuszczalna wartość! Maksymalna waga jest mniejsza niż minimalna waga</t>
+  </si>
+  <si>
+    <t>Niedopuszczalna wartość! Minimalna waga jest większa niż maksymalna waga</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! ¡El valor de consigna es mayor que la magnitud de referencia!</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! ¡El nivel de alarma es inferior al peso máximo!</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! ¡El peso máximo es inferior al peso mínimo!</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! ¡El peso mínimo es mayor que el peso máximo!</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Заданное значение превышает эталонное значение!</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Уровень сигнализации ниже максимального веса</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Максимальный вес меньше минимального веса</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Минимальный вес превышает максимальный вес</t>
+  </si>
+  <si>
+    <t>值超出允许范围！设定值大于参考值！</t>
+  </si>
+  <si>
+    <t>值超出允许范围！报警阈值小于最大重量</t>
+  </si>
+  <si>
+    <t>值超出允许范围！最大重量小于最小重量</t>
+  </si>
+  <si>
+    <t>值超出允许范围！最小重量大于最大重量</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Задане значення перевищує опорне значення!</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Рівень тривоги нижчий за максимальну вагу</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Максимальна вага менша за мінімальну вагу</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Мінімальна вага перевищує максимальну вагу</t>
+  </si>
+  <si>
+    <t>Nem megengedett érték! A beállított érték nagyobb, mint a referenciaérték!</t>
+  </si>
+  <si>
+    <t>Nem megengedett érték! A riasztási szint kisebb, mint a maximális súly</t>
+  </si>
+  <si>
+    <t>Nem megengedett érték! A maximális súly kisebb, mint a minimális súly</t>
+  </si>
+  <si>
+    <t>Nem megengedett érték! A minimális súly nagyobb, mint a maximális súly</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Η τιμή-στόχος είναι μεγαλύτερη από την τιμή αναφοράς!</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Το επίπεδο συναγερμού είναι μικρότερο από το μέγιστο βάρος</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Το μέγιστο βάρος είναι μικρότερο από το ελάχιστο βάρος</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Το ελάχιστο βάρος είναι μεγαλύτερο από το μέγιστο βάρος</t>
   </si>
 </sst>
 </file>
@@ -32172,7 +32329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M861"/>
+  <dimension ref="A1:M865"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.33203125" style="1" customWidth="1"/>
@@ -67483,6 +67640,170 @@
         <v>10407</v>
       </c>
     </row>
+    <row r="862" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A862" s="1" t="s">
+        <v>10408</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>10412</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>10416</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>10420</v>
+      </c>
+      <c r="E862" s="1" t="s">
+        <v>10424</v>
+      </c>
+      <c r="F862" s="1" t="s">
+        <v>10428</v>
+      </c>
+      <c r="G862" s="1" t="s">
+        <v>10432</v>
+      </c>
+      <c r="H862" s="1" t="s">
+        <v>10436</v>
+      </c>
+      <c r="I862" s="2" t="s">
+        <v>10440</v>
+      </c>
+      <c r="J862" s="1" t="s">
+        <v>10444</v>
+      </c>
+      <c r="K862" s="1" t="s">
+        <v>10448</v>
+      </c>
+      <c r="L862" s="1" t="s">
+        <v>10452</v>
+      </c>
+      <c r="M862" s="1" t="s">
+        <v>10456</v>
+      </c>
+    </row>
+    <row r="863" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A863" s="1" t="s">
+        <v>10409</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>10413</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>10417</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>10421</v>
+      </c>
+      <c r="E863" s="1" t="s">
+        <v>10425</v>
+      </c>
+      <c r="F863" s="1" t="s">
+        <v>10429</v>
+      </c>
+      <c r="G863" s="1" t="s">
+        <v>10433</v>
+      </c>
+      <c r="H863" s="1" t="s">
+        <v>10437</v>
+      </c>
+      <c r="I863" s="2" t="s">
+        <v>10441</v>
+      </c>
+      <c r="J863" s="1" t="s">
+        <v>10445</v>
+      </c>
+      <c r="K863" s="1" t="s">
+        <v>10449</v>
+      </c>
+      <c r="L863" s="1" t="s">
+        <v>10453</v>
+      </c>
+      <c r="M863" s="1" t="s">
+        <v>10457</v>
+      </c>
+    </row>
+    <row r="864" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A864" s="1" t="s">
+        <v>10410</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>10414</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>10418</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>10422</v>
+      </c>
+      <c r="E864" s="1" t="s">
+        <v>10426</v>
+      </c>
+      <c r="F864" s="1" t="s">
+        <v>10430</v>
+      </c>
+      <c r="G864" s="1" t="s">
+        <v>10434</v>
+      </c>
+      <c r="H864" s="1" t="s">
+        <v>10438</v>
+      </c>
+      <c r="I864" s="2" t="s">
+        <v>10442</v>
+      </c>
+      <c r="J864" s="1" t="s">
+        <v>10446</v>
+      </c>
+      <c r="K864" s="1" t="s">
+        <v>10450</v>
+      </c>
+      <c r="L864" s="1" t="s">
+        <v>10454</v>
+      </c>
+      <c r="M864" s="1" t="s">
+        <v>10458</v>
+      </c>
+    </row>
+    <row r="865" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A865" s="1" t="s">
+        <v>10411</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>10415</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>10419</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>10423</v>
+      </c>
+      <c r="E865" s="1" t="s">
+        <v>10427</v>
+      </c>
+      <c r="F865" s="1" t="s">
+        <v>10431</v>
+      </c>
+      <c r="G865" s="1" t="s">
+        <v>10435</v>
+      </c>
+      <c r="H865" s="1" t="s">
+        <v>10439</v>
+      </c>
+      <c r="I865" s="2" t="s">
+        <v>10443</v>
+      </c>
+      <c r="J865" s="1" t="s">
+        <v>10447</v>
+      </c>
+      <c r="K865" s="1" t="s">
+        <v>10451</v>
+      </c>
+      <c r="L865" s="1" t="s">
+        <v>10455</v>
+      </c>
+      <c r="M865" s="1" t="s">
+        <v>10459</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Language/EasyControlLang.xlsx
+++ b/Language/EasyControlLang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEVELOP\Cplusplus\SmaDoTec\Language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEACEE7-E2F6-4638-B3ED-6E8B04292214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFBEA26-7A40-47F0-8750-7B17224F7D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22440" yWindow="2190" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25140" yWindow="1380" windowWidth="21885" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EasyControlLang" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11242" uniqueCount="10460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11333" uniqueCount="10547">
   <si>
     <t>Deutsch</t>
   </si>
@@ -31429,12 +31429,273 @@
   <si>
     <t>Μη επιτρεπόμενη τιμή! Το ελάχιστο βάρος είναι μεγαλύτερο από το μέγιστο βάρος</t>
   </si>
+  <si>
+    <t>Sollwert beim Erreichen des Max. Gewichts</t>
+  </si>
+  <si>
+    <t>Sollwert Maxgrenze [kg/h]</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Nominaler Sollwert ist größer als Bezugsgröße</t>
+  </si>
+  <si>
+    <t>Autostart</t>
+  </si>
+  <si>
+    <t>Nominalsollwert</t>
+  </si>
+  <si>
+    <t>Die IFL-Sollwertregelung startet, sobald mindestens ein Dosierer gestartet wurde</t>
+  </si>
+  <si>
+    <t>Der Nominalsollwert wird eingestellt, wenn der Gewichtswert unter das Min-Gewicht fällt</t>
+  </si>
+  <si>
+    <t>Setpoint when maximum weight is reached</t>
+  </si>
+  <si>
+    <t>Maximum limit setpoint [kg/h]</t>
+  </si>
+  <si>
+    <t>Invalid value! Nominal setpoint is greater than the reference value</t>
+  </si>
+  <si>
+    <t>Nominal setpoint</t>
+  </si>
+  <si>
+    <t>The IFL setpoint control starts as soon as at least one feeder has been started</t>
+  </si>
+  <si>
+    <t>The nominal setpoint is set when the weight value falls below the minimum weight</t>
+  </si>
+  <si>
+    <t>Valeur de consigne lorsque le poids maximal est atteint</t>
+  </si>
+  <si>
+    <t>Valeur de consigne limite maximale [kg/h]</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! La valeur de consigne nominale est supérieure à la valeur de référence</t>
+  </si>
+  <si>
+    <t>Démarrage automatique</t>
+  </si>
+  <si>
+    <t>Valeur de consigne nominale</t>
+  </si>
+  <si>
+    <t>La régulation de la valeur de consigne IFL démarre dès qu’au moins un doseur a été mis en marche</t>
+  </si>
+  <si>
+    <t>La valeur de consigne nominale est réglée lorsque la valeur de poids passe en dessous du poids minimal</t>
+  </si>
+  <si>
+    <t>Valore di setpoint al raggiungimento del peso massimo</t>
+  </si>
+  <si>
+    <t>Valore di setpoint limite massimo [kg/h]</t>
+  </si>
+  <si>
+    <t>Valore non consentito! Il valore di setpoint nominale è superiore al valore di riferimento</t>
+  </si>
+  <si>
+    <t>Avvio automatico</t>
+  </si>
+  <si>
+    <t>Valore di setpoint nominale</t>
+  </si>
+  <si>
+    <t>La regolazione del setpoint IFL si avvia non appena viene avviato almeno un dosatore</t>
+  </si>
+  <si>
+    <t>Il valore di setpoint nominale viene impostato quando il valore di peso scende al di sotto del peso minimo</t>
+  </si>
+  <si>
+    <t>Streefwaarde bij het bereiken van het maximale gewicht</t>
+  </si>
+  <si>
+    <t>Streefwaarde maximale grens [kg/h]</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! Nominale streefwaarde is groter dan de referentiewaarde</t>
+  </si>
+  <si>
+    <t>Nominale streefwaarde</t>
+  </si>
+  <si>
+    <t>De IFL-streefwaarderegeling start zodra ten minste één doseerder is gestart</t>
+  </si>
+  <si>
+    <t>De nominale streefwaarde wordt ingesteld wanneer de gewichtswaarde onder het minimumgewicht daalt</t>
+  </si>
+  <si>
+    <t>Maks. ağırlığa ulaşıldığında ayar değeri</t>
+  </si>
+  <si>
+    <t>Maks. sınır ayar değeri [kg/h]</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Nominal ayar değeri referans değerinden büyük</t>
+  </si>
+  <si>
+    <t>Otomatik başlatma</t>
+  </si>
+  <si>
+    <t>Nominal ayar değeri</t>
+  </si>
+  <si>
+    <t>En az bir dozlayıcı çalıştırıldığında IFL ayar değeri kontrolü başlar</t>
+  </si>
+  <si>
+    <t>Ağırlık değeri minimum ağırlığın altına düştüğünde nominal ayar değeri ayarlanır</t>
+  </si>
+  <si>
+    <t>Wartość zadana po osiągnięciu maksymalnej masy</t>
+  </si>
+  <si>
+    <t>Wartość zadana – limit maksymalny [kg/h]</t>
+  </si>
+  <si>
+    <t>Wartość niedopuszczalna! Nominalna wartość zadana jest większa niż wartość odniesienia</t>
+  </si>
+  <si>
+    <t>Nominalna wartość zadana</t>
+  </si>
+  <si>
+    <t>Regulacja wartości zadanej IFL uruchamia się, gdy tylko uruchomiony zostanie co najmniej jeden dozownik</t>
+  </si>
+  <si>
+    <t>Nominalna wartość zadana jest ustawiana, gdy wartość masy spadnie poniżej masy minimalnej</t>
+  </si>
+  <si>
+    <t>Valor de consigna al alcanzar el peso máximo</t>
+  </si>
+  <si>
+    <t>Valor de consigna del límite máximo [kg/h]</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! El valor de consigna nominal es mayor que el valor de referencia</t>
+  </si>
+  <si>
+    <t>Arranque automático</t>
+  </si>
+  <si>
+    <t>Valor de consigna nominal</t>
+  </si>
+  <si>
+    <t>El control de consigna IFL se inicia en cuanto se pone en marcha al menos un dosificador</t>
+  </si>
+  <si>
+    <t>El valor de consigna nominal se ajusta cuando el valor de peso cae por debajo del peso mínimo</t>
+  </si>
+  <si>
+    <t>Заданное значение при достижении максимального веса</t>
+  </si>
+  <si>
+    <t>Заданное значение максимального предела [кг/ч]</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Номинальное заданное значение превышает эталонное значение</t>
+  </si>
+  <si>
+    <t>Автозапуск</t>
+  </si>
+  <si>
+    <t>Номинальное заданное значение</t>
+  </si>
+  <si>
+    <t>Регулирование по заданному значению IFL запускается, как только запущен хотя бы один дозатор</t>
+  </si>
+  <si>
+    <t>Номинальное заданное значение устанавливается, когда значение веса опускается ниже минимального веса</t>
+  </si>
+  <si>
+    <t>达到最大重量时的设定值</t>
+  </si>
+  <si>
+    <t>最大限值设定值 [kg/h]</t>
+  </si>
+  <si>
+    <t>值超出范围！标称设定值大于参考值</t>
+  </si>
+  <si>
+    <t>自动启动</t>
+  </si>
+  <si>
+    <t>标称设定值</t>
+  </si>
+  <si>
+    <t>只要至少有一台计量器启动，IFL设定值控制即开始运行</t>
+  </si>
+  <si>
+    <t>当重量值低于最小重量时，将设置标称设定值</t>
+  </si>
+  <si>
+    <t>Значення заданої величини при досягненні максимальної ваги</t>
+  </si>
+  <si>
+    <t>Значення заданої величини — максимальне обмеження [кг/год]</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Номінальне значення заданої величини перевищує опорне значення</t>
+  </si>
+  <si>
+    <t>Номінальне значення заданої величини</t>
+  </si>
+  <si>
+    <t>Регулювання за заданою величиною IFL запускається, щойно запущено хоча б один дозатор</t>
+  </si>
+  <si>
+    <t>Номінальне значення заданої величини встановлюється, коли значення ваги опускається нижче мінімальної ваги</t>
+  </si>
+  <si>
+    <t>Beállított érték a maximális tömeg elérésekor</t>
+  </si>
+  <si>
+    <t>Beállított érték: maximális határ [kg/h]</t>
+  </si>
+  <si>
+    <t>Nem megengedett érték! A névleges beállított érték nagyobb, mint a referenciaérték</t>
+  </si>
+  <si>
+    <t>Automatikus indítás</t>
+  </si>
+  <si>
+    <t>Névleges beállított érték</t>
+  </si>
+  <si>
+    <t>Az IFL-beállított érték-szabályozás elindul, amint legalább egy adagoló elindult</t>
+  </si>
+  <si>
+    <t>A névleges beállított érték beállításra kerül, ha a tömegérték a minimális tömeg alá csökken</t>
+  </si>
+  <si>
+    <t>Τιμή ρύθμισης κατά την επίτευξη του μέγιστου βάρους</t>
+  </si>
+  <si>
+    <t>Τιμή ρύθμισης ανώτατου ορίου [kg/h]</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Η ονομαστική τιμή ρύθμισης είναι μεγαλύτερη από την τιμή αναφοράς</t>
+  </si>
+  <si>
+    <t>Αυτόματη εκκίνηση</t>
+  </si>
+  <si>
+    <t>Ονομαστική τιμή ρύθμισης</t>
+  </si>
+  <si>
+    <t>Ο έλεγχος τιμής ρύθμισης IFL ξεκινά μόλις τεθεί σε λειτουργία τουλάχιστον ένας δοσομετρητής</t>
+  </si>
+  <si>
+    <t>Η ονομαστική τιμή ρύθμισης ρυθμίζεται όταν η τιμή βάρους πέσει κάτω από το ελάχιστο βάρος</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -31599,6 +31860,14 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -31901,7 +32170,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -31944,8 +32213,9 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -31974,8 +32244,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -32006,6 +32277,7 @@
     <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Link" xfId="42" builtinId="8"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
@@ -32329,7 +32601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M865"/>
+  <dimension ref="A1:M882"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.33203125" style="1" customWidth="1"/>
@@ -67804,6 +68076,323 @@
         <v>10459</v>
       </c>
     </row>
+    <row r="866" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A866" s="1" t="s">
+        <v>10460</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>10467</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>10473</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>10480</v>
+      </c>
+      <c r="E866" s="1" t="s">
+        <v>10487</v>
+      </c>
+      <c r="F866" s="1" t="s">
+        <v>10493</v>
+      </c>
+      <c r="G866" s="1" t="s">
+        <v>10500</v>
+      </c>
+      <c r="H866" s="1" t="s">
+        <v>10506</v>
+      </c>
+      <c r="I866" s="2" t="s">
+        <v>10513</v>
+      </c>
+      <c r="J866" s="1" t="s">
+        <v>10520</v>
+      </c>
+      <c r="K866" s="1" t="s">
+        <v>10527</v>
+      </c>
+      <c r="L866" s="1" t="s">
+        <v>10533</v>
+      </c>
+      <c r="M866" s="1" t="s">
+        <v>10540</v>
+      </c>
+    </row>
+    <row r="867" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A867" s="1" t="s">
+        <v>10461</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>10468</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>10474</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>10481</v>
+      </c>
+      <c r="E867" s="1" t="s">
+        <v>10488</v>
+      </c>
+      <c r="F867" s="1" t="s">
+        <v>10494</v>
+      </c>
+      <c r="G867" s="1" t="s">
+        <v>10501</v>
+      </c>
+      <c r="H867" s="1" t="s">
+        <v>10507</v>
+      </c>
+      <c r="I867" s="2" t="s">
+        <v>10514</v>
+      </c>
+      <c r="J867" s="1" t="s">
+        <v>10521</v>
+      </c>
+      <c r="K867" s="1" t="s">
+        <v>10528</v>
+      </c>
+      <c r="L867" s="1" t="s">
+        <v>10534</v>
+      </c>
+      <c r="M867" s="1" t="s">
+        <v>10541</v>
+      </c>
+    </row>
+    <row r="868" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A868" s="1" t="s">
+        <v>10462</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>10469</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>10475</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>10482</v>
+      </c>
+      <c r="E868" s="1" t="s">
+        <v>10489</v>
+      </c>
+      <c r="F868" s="1" t="s">
+        <v>10495</v>
+      </c>
+      <c r="G868" s="1" t="s">
+        <v>10502</v>
+      </c>
+      <c r="H868" s="1" t="s">
+        <v>10508</v>
+      </c>
+      <c r="I868" s="2" t="s">
+        <v>10515</v>
+      </c>
+      <c r="J868" s="1" t="s">
+        <v>10522</v>
+      </c>
+      <c r="K868" s="1" t="s">
+        <v>10529</v>
+      </c>
+      <c r="L868" s="1" t="s">
+        <v>10535</v>
+      </c>
+      <c r="M868" s="1" t="s">
+        <v>10542</v>
+      </c>
+    </row>
+    <row r="869" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A869" s="1" t="s">
+        <v>10463</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>10463</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>10476</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>10483</v>
+      </c>
+      <c r="E869" s="1" t="s">
+        <v>10463</v>
+      </c>
+      <c r="F869" s="1" t="s">
+        <v>10496</v>
+      </c>
+      <c r="G869" s="1" t="s">
+        <v>10463</v>
+      </c>
+      <c r="H869" s="1" t="s">
+        <v>10509</v>
+      </c>
+      <c r="I869" s="2" t="s">
+        <v>10516</v>
+      </c>
+      <c r="J869" s="1" t="s">
+        <v>10523</v>
+      </c>
+      <c r="K869" s="1" t="s">
+        <v>10516</v>
+      </c>
+      <c r="L869" s="1" t="s">
+        <v>10536</v>
+      </c>
+      <c r="M869" s="1" t="s">
+        <v>10543</v>
+      </c>
+    </row>
+    <row r="870" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A870" s="1" t="s">
+        <v>10464</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>10470</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>10477</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>10484</v>
+      </c>
+      <c r="E870" s="1" t="s">
+        <v>10490</v>
+      </c>
+      <c r="F870" s="1" t="s">
+        <v>10497</v>
+      </c>
+      <c r="G870" s="1" t="s">
+        <v>10503</v>
+      </c>
+      <c r="H870" s="1" t="s">
+        <v>10510</v>
+      </c>
+      <c r="I870" s="2" t="s">
+        <v>10517</v>
+      </c>
+      <c r="J870" s="1" t="s">
+        <v>10524</v>
+      </c>
+      <c r="K870" s="1" t="s">
+        <v>10530</v>
+      </c>
+      <c r="L870" s="1" t="s">
+        <v>10537</v>
+      </c>
+      <c r="M870" s="1" t="s">
+        <v>10544</v>
+      </c>
+    </row>
+    <row r="871" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A871" s="1" t="s">
+        <v>10465</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>10471</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>10478</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>10485</v>
+      </c>
+      <c r="E871" s="1" t="s">
+        <v>10491</v>
+      </c>
+      <c r="F871" s="1" t="s">
+        <v>10498</v>
+      </c>
+      <c r="G871" s="1" t="s">
+        <v>10504</v>
+      </c>
+      <c r="H871" s="1" t="s">
+        <v>10511</v>
+      </c>
+      <c r="I871" s="2" t="s">
+        <v>10518</v>
+      </c>
+      <c r="J871" s="1" t="s">
+        <v>10525</v>
+      </c>
+      <c r="K871" s="1" t="s">
+        <v>10531</v>
+      </c>
+      <c r="L871" s="1" t="s">
+        <v>10538</v>
+      </c>
+      <c r="M871" s="1" t="s">
+        <v>10545</v>
+      </c>
+    </row>
+    <row r="872" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A872" s="1" t="s">
+        <v>10466</v>
+      </c>
+      <c r="B872" s="1" t="s">
+        <v>10472</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>10479</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>10486</v>
+      </c>
+      <c r="E872" s="1" t="s">
+        <v>10492</v>
+      </c>
+      <c r="F872" s="1" t="s">
+        <v>10499</v>
+      </c>
+      <c r="G872" s="1" t="s">
+        <v>10505</v>
+      </c>
+      <c r="H872" s="1" t="s">
+        <v>10512</v>
+      </c>
+      <c r="I872" s="2" t="s">
+        <v>10519</v>
+      </c>
+      <c r="J872" s="1" t="s">
+        <v>10526</v>
+      </c>
+      <c r="K872" s="1" t="s">
+        <v>10532</v>
+      </c>
+      <c r="L872" s="1" t="s">
+        <v>10539</v>
+      </c>
+      <c r="M872" s="1" t="s">
+        <v>10546</v>
+      </c>
+    </row>
+    <row r="873" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D873"/>
+    </row>
+    <row r="874" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D874"/>
+    </row>
+    <row r="875" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D875"/>
+    </row>
+    <row r="876" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D876"/>
+    </row>
+    <row r="877" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D877"/>
+    </row>
+    <row r="878" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D878"/>
+    </row>
+    <row r="879" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D879"/>
+    </row>
+    <row r="880" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D880"/>
+    </row>
+    <row r="881" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D881"/>
+    </row>
+    <row r="882" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D882" s="10"/>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Language/EasyControlLang.xlsx
+++ b/Language/EasyControlLang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEVELOP\Cplusplus\SmaDoTec\Language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFBEA26-7A40-47F0-8750-7B17224F7D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927B5E0D-B2FC-4D55-B974-3CDB9F167A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25140" yWindow="1380" windowWidth="21885" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EasyControlLang" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11333" uniqueCount="10547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11398" uniqueCount="10612">
   <si>
     <t>Deutsch</t>
   </si>
@@ -31689,6 +31689,201 @@
   </si>
   <si>
     <t>Η ονομαστική τιμή ρύθμισης ρυθμίζεται όταν η τιμή βάρους πέσει κάτω από το ελάχιστο βάρος</t>
+  </si>
+  <si>
+    <t>Alarmpegel Überlauf [kg]</t>
+  </si>
+  <si>
+    <t>Nominalsollwert [kg/h]</t>
+  </si>
+  <si>
+    <t>Sollwert bei Max. Gewicht [kg/h]</t>
+  </si>
+  <si>
+    <t>Beim Erreichen des Alarmpegels bei Überlauf wird der Liniensollwert auf 0 gesetzt und die Dosierer gestoppt</t>
+  </si>
+  <si>
+    <t>Unzulässiger Wert! Nominalsollwert kleiner als Sollwert bei Max.Gewicht</t>
+  </si>
+  <si>
+    <t>Overflow Alarm Level [kg]</t>
+  </si>
+  <si>
+    <t>Nominal Setpoint [kg/h]</t>
+  </si>
+  <si>
+    <t>Setpoint at Max. Weight [kg/h]</t>
+  </si>
+  <si>
+    <t>When the overflow alarm level is reached, the line setpoint is set to 0 and the feeders are stopped</t>
+  </si>
+  <si>
+    <t>Invalid value! Nominal setpoint is less than the setpoint at max. weight</t>
+  </si>
+  <si>
+    <t>Seuil d'alarme de débordement [kg]</t>
+  </si>
+  <si>
+    <t>Consigne nominale [kg/h]</t>
+  </si>
+  <si>
+    <t>Consigne au poids maximal [kg/h]</t>
+  </si>
+  <si>
+    <t>Lorsque le seuil d'alarme de débordement est atteint, la consigne de ligne est remise à 0 et les doseurs sont arrêtés</t>
+  </si>
+  <si>
+    <t>Valeur non autorisée ! Consigne nominale inférieure à la consigne au poids maximal</t>
+  </si>
+  <si>
+    <t>Livello di allarme di trabocco [kg]</t>
+  </si>
+  <si>
+    <t>Valore nominale di riferimento [kg/h]</t>
+  </si>
+  <si>
+    <t>Valore di riferimento al peso massimo [kg/h]</t>
+  </si>
+  <si>
+    <t>Quando viene raggiunto il livello di allarme di trabocco, il valore di riferimento della linea viene impostato a 0 e i dosatori vengono arrestati</t>
+  </si>
+  <si>
+    <t>Valore non consentito! Valore nominale di riferimento inferiore al valore di riferimento al peso massimo</t>
+  </si>
+  <si>
+    <t>Alarmniveau overloop [kg]</t>
+  </si>
+  <si>
+    <t>Nominale instelwaarde [kg/h]</t>
+  </si>
+  <si>
+    <t>Instelwaarde bij max. gewicht [kg/h]</t>
+  </si>
+  <si>
+    <t>Wanneer het alarmniveau voor overloop wordt bereikt, wordt de lijninstelwaarde op 0 gezet en worden de doseerapparaten gestopt</t>
+  </si>
+  <si>
+    <t>Ongeldige waarde! Nominale instelwaarde kleiner dan instelwaarde bij max. gewicht</t>
+  </si>
+  <si>
+    <t>Taşma Alarm Seviyesi [kg]</t>
+  </si>
+  <si>
+    <t>Nominal Ayar Değeri [kg/h]</t>
+  </si>
+  <si>
+    <t>Maks. Ağırlıkta Ayar Değeri [kg/h]</t>
+  </si>
+  <si>
+    <t>Taşma alarm seviyesine ulaşıldığında, hat ayar değeri 0’a ayarlanır ve dozlayıcılar durdurulur</t>
+  </si>
+  <si>
+    <t>Geçerli olmayan değer! Nominal ayar değeri, Maks. Ağırlıkta Ayar Değeri’nden daha düşük</t>
+  </si>
+  <si>
+    <t>Poziom alarmowy przepełnienia [kg]</t>
+  </si>
+  <si>
+    <t>Nominalna wartość zadana [kg/h]</t>
+  </si>
+  <si>
+    <t>Wartość zadana przy maksymalnej masie [kg/h]</t>
+  </si>
+  <si>
+    <t>Po osiągnięciu poziomu alarmowego przepełnienia wartość zadana linii zostaje ustawiona na 0, a dozowniki zostają zatrzymane</t>
+  </si>
+  <si>
+    <t>Niedopuszczalna wartość! Nominalna wartość zadana mniejsza niż wartość zadana przy maksymalnej masie</t>
+  </si>
+  <si>
+    <t>Nivel de alarma de desbordamiento [kg]</t>
+  </si>
+  <si>
+    <t>Valor nominal de consigna [kg/h]</t>
+  </si>
+  <si>
+    <t>Valor de consigna con peso máximo [kg/h]</t>
+  </si>
+  <si>
+    <t>Cuando se alcanza el nivel de alarma de desbordamiento, el valor de consigna de la línea se establece en 0 y se detienen los dosificadores</t>
+  </si>
+  <si>
+    <t>¡Valor no válido! El valor nominal de consigna es inferior al valor de consigna con peso máximo</t>
+  </si>
+  <si>
+    <t>Уровень сигнализации переполнения [кг]</t>
+  </si>
+  <si>
+    <t>Номинальное заданное значение [кг/ч]</t>
+  </si>
+  <si>
+    <t>Заданное значение при максимальном весе [кг/ч]</t>
+  </si>
+  <si>
+    <t>При достижении уровня сигнализации переполнения заданное значение линии устанавливается на 0, а дозаторы останавливаются</t>
+  </si>
+  <si>
+    <t>Недопустимое значение! Номинальное заданное значение меньше заданного значения при максимальном весе</t>
+  </si>
+  <si>
+    <t>溢出报警阈值 [kg]</t>
+  </si>
+  <si>
+    <t>额定设定值 [kg/h]</t>
+  </si>
+  <si>
+    <t>最大重量下的设定值 [kg/h]</t>
+  </si>
+  <si>
+    <t>当达到溢出报警阈值时，生产线设定值将设为0，且计量器将停止运行</t>
+  </si>
+  <si>
+    <t>值不合法！额定设定值小于最大重量下的设定值</t>
+  </si>
+  <si>
+    <t>Рівень тривоги переповнення [кг]</t>
+  </si>
+  <si>
+    <t>Номінальне задане значення [кг/год]</t>
+  </si>
+  <si>
+    <t>Задане значення при максимальній вазі [кг/год]</t>
+  </si>
+  <si>
+    <t>При досягненні рівня тривоги переповнення задане значення лінії встановлюється на 0, а дозатори зупиняються</t>
+  </si>
+  <si>
+    <t>Недопустиме значення! Номінальне задане значення менше, ніж задане значення при максимальній вазі</t>
+  </si>
+  <si>
+    <t>Túlcsordulási riasztási szint [kg]</t>
+  </si>
+  <si>
+    <t>Névleges beállítási érték [kg/h]</t>
+  </si>
+  <si>
+    <t>Beállítási érték maximális tömeg esetén [kg/h]</t>
+  </si>
+  <si>
+    <t>A túlcsordulási riasztási szint elérésekor a vonali beállítási érték 0-ra áll, és az adagolók leállnak</t>
+  </si>
+  <si>
+    <t>Megengedhetetlen érték! A névleges beállítási érték kisebb, mint a maximális tömeg esetén érvényes beállítási érték</t>
+  </si>
+  <si>
+    <t>Επίπεδο συναγερμού υπερχείλισης [kg]</t>
+  </si>
+  <si>
+    <t>Ονομαστική τιμή ρύθμισης [kg/h]</t>
+  </si>
+  <si>
+    <t>Τιμή ρύθμισης για μέγιστο βάρος [kg/h]</t>
+  </si>
+  <si>
+    <t>Όταν επιτευχθεί το επίπεδο συναγερμού υπερχείλισης, η τιμή ρύθμισης της γραμμής ορίζεται στο 0 και οι δοσομετρητές σταματούν</t>
+  </si>
+  <si>
+    <t>Μη επιτρεπόμενη τιμή! Η ονομαστική τιμή ρύθμισης είναι μικρότερη από την τιμή ρύθμισης για μέγιστο βάρος</t>
   </si>
 </sst>
 </file>
@@ -68363,20 +68558,210 @@
         <v>10546</v>
       </c>
     </row>
-    <row r="873" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D873"/>
-    </row>
-    <row r="874" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D874"/>
-    </row>
-    <row r="875" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D875"/>
-    </row>
-    <row r="876" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D876"/>
-    </row>
-    <row r="877" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D877"/>
+    <row r="873" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A873" s="1" t="s">
+        <v>10547</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>10552</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>10557</v>
+      </c>
+      <c r="D873" s="9" t="s">
+        <v>10562</v>
+      </c>
+      <c r="E873" s="1" t="s">
+        <v>10567</v>
+      </c>
+      <c r="F873" s="1" t="s">
+        <v>10572</v>
+      </c>
+      <c r="G873" s="1" t="s">
+        <v>10577</v>
+      </c>
+      <c r="H873" s="1" t="s">
+        <v>10582</v>
+      </c>
+      <c r="I873" s="2" t="s">
+        <v>10587</v>
+      </c>
+      <c r="J873" s="1" t="s">
+        <v>10592</v>
+      </c>
+      <c r="K873" s="1" t="s">
+        <v>10597</v>
+      </c>
+      <c r="L873" s="1" t="s">
+        <v>10602</v>
+      </c>
+      <c r="M873" s="1" t="s">
+        <v>10607</v>
+      </c>
+    </row>
+    <row r="874" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A874" s="1" t="s">
+        <v>10548</v>
+      </c>
+      <c r="B874" s="1" t="s">
+        <v>10553</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>10558</v>
+      </c>
+      <c r="D874" s="9" t="s">
+        <v>10563</v>
+      </c>
+      <c r="E874" s="1" t="s">
+        <v>10568</v>
+      </c>
+      <c r="F874" s="1" t="s">
+        <v>10573</v>
+      </c>
+      <c r="G874" s="1" t="s">
+        <v>10578</v>
+      </c>
+      <c r="H874" s="1" t="s">
+        <v>10583</v>
+      </c>
+      <c r="I874" s="2" t="s">
+        <v>10588</v>
+      </c>
+      <c r="J874" s="1" t="s">
+        <v>10593</v>
+      </c>
+      <c r="K874" s="1" t="s">
+        <v>10598</v>
+      </c>
+      <c r="L874" s="1" t="s">
+        <v>10603</v>
+      </c>
+      <c r="M874" s="1" t="s">
+        <v>10608</v>
+      </c>
+    </row>
+    <row r="875" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A875" s="1" t="s">
+        <v>10549</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>10554</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>10559</v>
+      </c>
+      <c r="D875" s="9" t="s">
+        <v>10564</v>
+      </c>
+      <c r="E875" s="1" t="s">
+        <v>10569</v>
+      </c>
+      <c r="F875" s="1" t="s">
+        <v>10574</v>
+      </c>
+      <c r="G875" s="1" t="s">
+        <v>10579</v>
+      </c>
+      <c r="H875" s="1" t="s">
+        <v>10584</v>
+      </c>
+      <c r="I875" s="2" t="s">
+        <v>10589</v>
+      </c>
+      <c r="J875" s="1" t="s">
+        <v>10594</v>
+      </c>
+      <c r="K875" s="1" t="s">
+        <v>10599</v>
+      </c>
+      <c r="L875" s="1" t="s">
+        <v>10604</v>
+      </c>
+      <c r="M875" s="1" t="s">
+        <v>10609</v>
+      </c>
+    </row>
+    <row r="876" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A876" s="1" t="s">
+        <v>10550</v>
+      </c>
+      <c r="B876" s="1" t="s">
+        <v>10555</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>10560</v>
+      </c>
+      <c r="D876" s="9" t="s">
+        <v>10565</v>
+      </c>
+      <c r="E876" s="1" t="s">
+        <v>10570</v>
+      </c>
+      <c r="F876" s="1" t="s">
+        <v>10575</v>
+      </c>
+      <c r="G876" s="1" t="s">
+        <v>10580</v>
+      </c>
+      <c r="H876" s="1" t="s">
+        <v>10585</v>
+      </c>
+      <c r="I876" s="2" t="s">
+        <v>10590</v>
+      </c>
+      <c r="J876" s="1" t="s">
+        <v>10595</v>
+      </c>
+      <c r="K876" s="1" t="s">
+        <v>10600</v>
+      </c>
+      <c r="L876" s="1" t="s">
+        <v>10605</v>
+      </c>
+      <c r="M876" s="1" t="s">
+        <v>10610</v>
+      </c>
+    </row>
+    <row r="877" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A877" s="1" t="s">
+        <v>10551</v>
+      </c>
+      <c r="B877" s="1" t="s">
+        <v>10556</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>10561</v>
+      </c>
+      <c r="D877" s="9" t="s">
+        <v>10566</v>
+      </c>
+      <c r="E877" s="1" t="s">
+        <v>10571</v>
+      </c>
+      <c r="F877" s="1" t="s">
+        <v>10576</v>
+      </c>
+      <c r="G877" s="1" t="s">
+        <v>10581</v>
+      </c>
+      <c r="H877" s="1" t="s">
+        <v>10586</v>
+      </c>
+      <c r="I877" s="2" t="s">
+        <v>10591</v>
+      </c>
+      <c r="J877" s="1" t="s">
+        <v>10596</v>
+      </c>
+      <c r="K877" s="1" t="s">
+        <v>10601</v>
+      </c>
+      <c r="L877" s="1" t="s">
+        <v>10606</v>
+      </c>
+      <c r="M877" s="1" t="s">
+        <v>10611</v>
+      </c>
     </row>
     <row r="878" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D878"/>
